--- a/Assets/Editor/ItemData/EquipItemDataBase.xlsx
+++ b/Assets/Editor/ItemData/EquipItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Editor\ItemData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93651C34-F79A-44BF-A32E-93D7031386BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC78C0D-3EEF-4117-9C60-7D09AF6363AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="1710" windowWidth="19845" windowHeight="11295" xr2:uid="{6EAF4D32-D501-4D72-AA72-8C2EEF7028C9}"/>
+    <workbookView xWindow="7350" yWindow="2460" windowWidth="19845" windowHeight="11295" xr2:uid="{6EAF4D32-D501-4D72-AA72-8C2EEF7028C9}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipItemDataBase" sheetId="1" r:id="rId1"/>
